--- a/survey_templates/038_journalistic_knowledge_quiz--survey_templates.xlsx
+++ b/survey_templates/038_journalistic_knowledge_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>field_1</t>
+          <t>journalismskills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>quiz questions</t>
+          <t>Journalistic Skills</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quiz_questions</t>
+          <t>criticalthinking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>quiz questions</t>
+          <t>Critical Thinking</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>quiz_questions</t>
+          <t>ethics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>quiz questions</t>
+          <t>Journalistic Ethics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>quiz_question</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>quiz questions</t>
+          <t>Storytelling</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>quiz_questions_5</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>quiz questions 5</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>quiz_question</t>
+          <t>writing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>quiz question 6</t>
+          <t>Writing</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>quiz_questions_7</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>quiz questions 7</t>
+          <t>Media and Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>quiz_question</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>quiz questions</t>
+          <t>Business and Law</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>quiz_questions_9</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>quiz questions 9</t>
+          <t>Leadership and Teamwork</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>quiz_question</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>quiz questions</t>
+          <t>Time Management</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>quiz_questions_11</t>
+          <t>career</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>quiz questions 11</t>
+          <t>Career Development</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>quiz_question_12</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>quiz question 12</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>quiz_questions_13</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>quiz questions 13</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>quiz_question_14</t>
+          <t>collaboration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>quiz question 14</t>
+          <t>Collaboration</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>quiz_question_15</t>
+          <t>self_maintenance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>quiz questions 15</t>
+          <t>Self-Care and Burnout</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>quiz_question_16</t>
+          <t>diversity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>quiz question 16</t>
+          <t>Diversity, Equity, and Inclusion</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>quiz_question_17</t>
+          <t>digitaltools</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>quiz questions 17</t>
+          <t>Digital Tools</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>quiz_question_18</t>
+          <t>digitalmedia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>quiz question 18</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>quiz_questions_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>quiz questions 19</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>quiz_question_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>quiz question 20</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>quiz_question_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>quiz questions 21</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>quiz_questions_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>quiz questions 22</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>quiz_question_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>quiz questions 23</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>quiz_questions_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>quiz questions 24</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>quiz_question_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>quiz questions 25</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,850 +965,918 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>field_1_choices</t>
+          <t>journalismskills_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>investigative_reporting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Investigative reporting</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>field_1_choices</t>
+          <t>journalismskills_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>in-depth_research</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>In-depth research</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quiz_questions_choices</t>
+          <t>journalismskills_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fact-checking</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fact-checking</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quiz_questions_choices</t>
+          <t>criticalthinking_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>analyzing_information</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Analyzing information</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quiz_questions_choices</t>
+          <t>criticalthinking_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>evaluating_evidence</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Evaluating evidence</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quiz_questions_choices</t>
+          <t>criticalthinking_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>considering_multiple_perspectives</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Considering multiple perspectives</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>ethics_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>respecting_sources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Respecting sources</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>ethics_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>maintaining_objectivity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Maintaining objectivity</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quiz_questions_5_choices</t>
+          <t>ethics_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>being_transparent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Being transparent</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quiz_questions_5_choices</t>
+          <t>storytelling_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>crafting_narratives</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Crafting narratives</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>storytelling_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>capturing_attention</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Capturing attention</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>storytelling_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>conveying_messages</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Conveying messages</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>quiz_questions_7_choices</t>
+          <t>reporting_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>gathering_information</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Gathering information</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>quiz_questions_7_choices</t>
+          <t>reporting_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>conducting_interviews</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Conducting interviews</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>reporting_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fact-checking</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fact-checking</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>writing_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>writing_clearly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Writing clearly</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>quiz_questions_9_choices</t>
+          <t>writing_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>writing_concisely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Writing concisely</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>quiz_questions_9_choices</t>
+          <t>writing_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>writing_objectively</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Writing objectively</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>media_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>using_social_media</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Using social media</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>media_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>creating_multimedia_content</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Creating multimedia content</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>quiz_questions_11_choices</t>
+          <t>media_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>understanding_media_law</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Understanding media law</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>quiz_questions_11_choices</t>
+          <t>business_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>understanding_business_models</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Understanding business models</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>quiz_question_12_choices</t>
+          <t>business_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>knowing_media_law</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Knowing media law</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>quiz_question_12_choices</t>
+          <t>business_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>managing_finances</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Managing finances</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>quiz_questions_13_choices</t>
+          <t>leadership_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>leading_a_team</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Leading a team</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>quiz_questions_13_choices</t>
+          <t>leadership_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>communicating_effectively</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Communicating effectively</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>quiz_question_14_choices</t>
+          <t>leadership_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>resolving_conflicts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Resolving conflicts</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>quiz_question_14_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>prioritizing_tasks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Prioritizing tasks</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>quiz_question_15_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>managing_deadlines</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Managing deadlines</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>quiz_question_15_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>minimizing_distractions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Minimizing distractions</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>quiz_question_16_choices</t>
+          <t>career_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>networking</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Networking</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>quiz_question_16_choices</t>
+          <t>career_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>building_relationships</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Building relationships</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>quiz_question_17_choices</t>
+          <t>career_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>continuing_education</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Continuing education</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>quiz_question_17_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>verbal_and_written_communication</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Verbal and written communication</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>quiz_question_18_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active_listening</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active listening</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>quiz_question_18_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>conflict_resolution</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Conflict resolution</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>quiz_questions_19_choices</t>
+          <t>research_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>conducting_research</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Conducting research</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>quiz_questions_19_choices</t>
+          <t>research_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>evaluating_sources</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Evaluating sources</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>quiz_question_20_choices</t>
+          <t>research_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>avoiding_plagiarism</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Avoiding plagiarism</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>quiz_question_20_choices</t>
+          <t>collaboration_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>collaborating_with_editors</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Collaborating with editors</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>quiz_question_21_choices</t>
+          <t>collaboration_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>working_with_colleagues</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Working with colleagues</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>quiz_question_21_choices</t>
+          <t>collaboration_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>respecting_others</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Respecting others</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quiz_questions_22_choices</t>
+          <t>self_maintenance_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>taking_breaks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Taking breaks</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>quiz_questions_22_choices</t>
+          <t>self_maintenance_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>staying_organized</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Staying organized</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>quiz_question_23_choices</t>
+          <t>self_maintenance_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>maintaining_a_healthy_work-life_balance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Maintaining a healthy work-life balance</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>quiz_question_23_choices</t>
+          <t>diversity_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>respecting_diverse_perspectives</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Respecting diverse perspectives</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>quiz_questions_24_choices</t>
+          <t>diversity_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>understanding_systemic_inequalities</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Understanding systemic inequalities</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>quiz_questions_24_choices</t>
+          <t>diversity_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>promoting_inclusivity</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Promoting inclusivity</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>quiz_question_25_choices</t>
+          <t>digitaltools_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>using_social_media</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Using social media</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>quiz_question_25_choices</t>
+          <t>digitaltools_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>creating_multimedia_content</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Creating multimedia content</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>digitaltools_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>analyzing_data</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Analyzing data</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>digitalmedia_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>creating_multimedia_content</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Creating multimedia content</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>digitalmedia_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>analyzing_data</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Analyzing data</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>digitalmedia_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>understanding_digital_media_law</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Understanding digital media law</t>
         </is>
       </c>
     </row>
